--- a/site/public/ig/CodeSystem-heartland-implementation-tier.xlsx
+++ b/site/public/ig/CodeSystem-heartland-implementation-tier.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T20:13:50-04:00</t>
+    <t>2026-09-17T14:02:25-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/public/ig/CodeSystem-heartland-implementation-tier.xlsx
+++ b/site/public/ig/CodeSystem-heartland-implementation-tier.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T14:02:25-04:00</t>
+    <t>2026-09-17T14:11:14-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/public/ig/CodeSystem-heartland-implementation-tier.xlsx
+++ b/site/public/ig/CodeSystem-heartland-implementation-tier.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="52">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,19 +48,19 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
   </si>
   <si>
-    <t>false</t>
+    <t>true</t>
   </si>
   <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T14:11:14-04:00</t>
+    <t>2026-09-29T19:00:36-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Facility implementation tiers from HEARTLAND Protocol v3.2 Module 8. Tiers reflect available resources (staffing, technology, financial navigation) and dictate which protocol components are operationally feasible at a given site.</t>
+    <t>Declared facility implementation capacity tiers, retaining historical code identities. Capacity informs delivery format, sequence and support; it does not determine clinical eligibility, permit delayed risk-led care or exclude educational domains. All eight domains are offered at every tier. These labels are not a scored readiness instrument or proof of actual coverage.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -102,9 +102,6 @@
     <t>Case Sensitive</t>
   </si>
   <si>
-    <t>true</t>
-  </si>
-  <si>
     <t>Value Set (all codes)</t>
   </si>
   <si>
@@ -153,7 +150,7 @@
     <t>Tier 1 - Minimal</t>
   </si>
   <si>
-    <t>Severely constrained settings, such as a small Critical Access Hospital with one to two nurses. Analog monitoring (Track B), condensed education domains, prioritized GDMT initiation.</t>
+    <t>Resource-constrained capacity. Adapt format, sequence and support; document gaps, named coverage, alternatives and escalation without omitting required care or relevant education.</t>
   </si>
   <si>
     <t>tier-2-standard</t>
@@ -162,7 +159,7 @@
     <t>Tier 2 - Standard</t>
   </si>
   <si>
-    <t>Moderate-resource settings, such as a Federally Qualified Health Center (FQHC) or community hospital. Dual-track monitoring (A/B), full education, target all GDMT classes within 14 days.</t>
+    <t>Intermediate implementation capacity with locally documented staffing, monitoring routes and navigation support. Capacity alone does not establish treatment sequence or deadlines.</t>
   </si>
   <si>
     <t>tier-3-advanced</t>
@@ -171,7 +168,7 @@
     <t>Tier 3 - Advanced</t>
   </si>
   <si>
-    <t>Well-resourced settings, such as a regional referral center. Track A primary with RPM, full multidisciplinary team, rapid-sequence GDMT initiation.</t>
+    <t>Expanded implementation capacity, potentially including multidisciplinary and digital support. The label alone does not prove availability, coverage, patient access or better outcomes.</t>
   </si>
 </sst>
 </file>
@@ -435,53 +432,53 @@
         <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B21" t="s" s="2">
         <v>34</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>35</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B23" t="s" s="2">
         <v>37</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -496,58 +493,58 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="B1" t="s" s="1">
         <v>39</v>
       </c>
-      <c r="B1" t="s" s="1">
+      <c r="C1" t="s" s="1">
         <v>40</v>
       </c>
-      <c r="C1" t="s" s="1">
+      <c r="D1" t="s" s="1">
         <v>41</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>42</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B2" t="s" s="2">
         <v>43</v>
       </c>
-      <c r="B2" t="s" s="2">
+      <c r="C2" t="s" s="2">
         <v>44</v>
       </c>
-      <c r="C2" t="s" s="2">
+      <c r="D2" t="s" s="2">
         <v>45</v>
-      </c>
-      <c r="D2" t="s" s="2">
-        <v>46</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="C3" t="s" s="2">
         <v>47</v>
       </c>
-      <c r="C3" t="s" s="2">
+      <c r="D3" t="s" s="2">
         <v>48</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>49</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B4" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="C4" t="s" s="2">
         <v>50</v>
       </c>
-      <c r="C4" t="s" s="2">
+      <c r="D4" t="s" s="2">
         <v>51</v>
-      </c>
-      <c r="D4" t="s" s="2">
-        <v>52</v>
       </c>
     </row>
   </sheetData>
